--- a/assets/constructions/examples/ctd_mih_hf.xlsx
+++ b/assets/constructions/examples/ctd_mih_hf.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG6"/>
+  <dimension ref="A1:AK6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -594,11 +594,31 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MHF-ENMX06-D42Z6M16</t>
+          <t>MHF-ENMX06-D25Z4M12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -612,27 +632,27 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="E2" t="n">
-        <v>34.6</v>
+        <v>17.6</v>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G2" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -652,7 +672,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>METRIC_THREAD:M16</t>
+          <t>METRIC_THREAD:M12</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -670,7 +690,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>M16</t>
+          <t>M12</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -687,6 +707,20 @@
           <t>2021/YG1-TOOLING</t>
         </is>
       </c>
+      <c r="AH2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>214.81</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AK2" t="n">
+        <v>19748.28</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -786,35 +820,45 @@
           <t>2019/ Основной каталог СКИФ-М</t>
         </is>
       </c>
+      <c r="AH3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>020R06410-02-02-M10025</t>
+          <t>MHF-ENMX06-D16Z2M08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PALBIT</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+          <t>YG1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ENMX 0604</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>16</v>
+      </c>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G4" t="n">
-        <v>16</v>
-      </c>
-      <c r="H4" t="n">
-        <v>25</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
@@ -824,47 +868,41 @@
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="n">
-        <v>0.04</v>
-      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>SOEW 080310 S/SOET 080315-MS</t>
+          <t>ENMX0604</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>METRIC_THREAD:M10</t>
+          <t>METRIC_THREAD:M8</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>PALB_SO0803H</t>
-        </is>
-      </c>
-      <c r="W4" t="n">
+          <t>YG1_EN0604H</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="n">
         <v>1</v>
       </c>
-      <c r="X4" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>M10</t>
+          <t>M08</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -872,67 +910,85 @@
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>PAL_SO0803_H</t>
+          <t>YG1_EN0604H</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2021/General catalogue</t>
-        </is>
+          <t>2021/YG1-TOOLING</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>162.19</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AK4" t="n">
+        <v>14910.73</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MT115-025G12R02FO09</t>
+          <t>VXF025Z04M12XP07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>СКИФ-М</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MT115-G...FO09</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>VXF-07</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>25</v>
+      </c>
       <c r="E5" t="n">
-        <v>25</v>
+        <v>15.64</v>
       </c>
       <c r="F5" t="n">
-        <v>12</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="n">
-        <v>57</v>
-      </c>
+        <v>12.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>21</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
         <v>35</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>49000</v>
+      </c>
       <c r="O5" t="n">
-        <v>0.3</v>
+        <v>0.09</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>FONT09T308..R</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="b">
+        <v>0</v>
+      </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
         <v>3</v>
@@ -944,7 +1000,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>SKIF_FO09T3H</t>
+          <t>WIDIA_XP0703H</t>
         </is>
       </c>
       <c r="W5" t="n">
@@ -954,10 +1010,10 @@
         <v>4</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -971,79 +1027,89 @@
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>SKIF_FO09T3H</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr"/>
+          <t>WID_XP0703_H</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>WID_VXF025_2813</t>
+        </is>
+      </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2019/ Основной каталог СКИФ-М</t>
-        </is>
-      </c>
+          <t>2019 / WIDIA достижения</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MT115-032G16R04FO09</t>
+          <t>ASR-25-M12-3T</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>СКИФ-М</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MT115-G...FO09</t>
+          <t>ASR</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F6" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="n">
-        <v>58</v>
-      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
         <v>35</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>0.5</v>
+        <v>0.14</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>FONT09T308..R</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
+          <t>EPNW0603TN-8</t>
+        </is>
+      </c>
+      <c r="R6" t="b">
+        <v>0</v>
+      </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="n">
         <v>3</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>METRIC_THREAD:M16</t>
+          <t>METRIC_THREAD:M12</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>SKIF_FO09T3H</t>
+          <t>DER_EP0603H</t>
         </is>
       </c>
       <c r="W6" t="n">
@@ -1060,24 +1126,36 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>M16</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>22</v>
-      </c>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>SKIF_FO09T3H</t>
+          <t>EP0603_H</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2019/ Основной каталог СКИФ-М</t>
-        </is>
+          <t>2019 / DEREK</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>89.09</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AK6" t="n">
+        <v>7303.05</v>
       </c>
     </row>
   </sheetData>
